--- a/Output/AllModels_SensitivityOnlyPushing_12000.xlsx
+++ b/Output/AllModels_SensitivityOnlyPushing_12000.xlsx
@@ -80,10 +80,10 @@
     <t xml:space="preserve">[49.25, 66.94]</t>
   </si>
   <si>
-    <t xml:space="preserve">124.23***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[110.58, 139.65]</t>
+    <t xml:space="preserve">124.24***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[110.38, 139.52]</t>
   </si>
   <si>
     <t xml:space="preserve">3.77***</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">[ 0.78,  1.05]</t>
   </si>
   <si>
-    <t xml:space="preserve">[  0.87,   1.08]</t>
+    <t xml:space="preserve">[  0.87,   1.07]</t>
   </si>
   <si>
     <t xml:space="preserve">0.28***</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">0.98</t>
   </si>
   <si>
-    <t xml:space="preserve">[  0.81,   1.17]</t>
+    <t xml:space="preserve">[  0.82,   1.17]</t>
   </si>
   <si>
     <t xml:space="preserve">0.12</t>

--- a/Output/AllModels_SensitivityOnlyPushing_12000.xlsx
+++ b/Output/AllModels_SensitivityOnlyPushing_12000.xlsx
@@ -1,475 +1,482 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kueng\DataAnalysis\02TimeAndTiesControl\Output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A4AB3A-7956-4524-82EE-CA08C4AB0C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjective MVPA Hurdle Lognormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device-Based MVPA Log (Gaussian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mood Gaussian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reactance Dichotome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurdle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.) pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 2.27,  6.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.42***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[49.25, 66.94]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.24***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[110.38, 139.52]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 3.54, 4.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.19,  0.67]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.17,  2.21]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.91,  1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.96,   1.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.06, 0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.06,  2.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.36,  2.74]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.90,  1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.98,   1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.00, 0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.78,  2.15]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.37,  0.99]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.78,  1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.87,   1.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.12, 0.44]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.49,  4.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  1.00,   1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Between-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.25,  0.83]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.99,  1.72]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.82,   1.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.21, 0.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.98***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[3.14, 58.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.32,  1.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.89,  1.55]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.87,   1.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.22, 0.43]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.51,  8.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.90, 1.73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.27, 0.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.08, 0.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.31, 0.73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.38, 2.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07, 1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.70]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.09, 1.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07, 0.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 1.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.21]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.17, 0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.38, 0.66]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.59, 2.33]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional Parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.64, 0.70]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.50, 0.54]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.81, 0.88]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="150">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Subjective MVPA Hurdle Lognormal</t>
+  </si>
+  <si>
+    <t>Device-Based MVPA Log (Gaussian)</t>
+  </si>
+  <si>
+    <t>Mood Gaussian</t>
+  </si>
+  <si>
+    <t>Reactance Dichotome</t>
+  </si>
+  <si>
+    <t>Hurdle</t>
+  </si>
+  <si>
+    <t>Non-Zero</t>
+  </si>
+  <si>
+    <t>exp(Est.)_hu pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_hu pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.)_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.) pa_obj_log</t>
+  </si>
+  <si>
+    <t>95% CI pa_obj_log</t>
+  </si>
+  <si>
+    <t>Est. mood_gauss</t>
+  </si>
+  <si>
+    <t>95% CI mood_gauss</t>
+  </si>
+  <si>
+    <t>OR is_reactance</t>
+  </si>
+  <si>
+    <t>95% CI is_reactance</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>3.80***</t>
+  </si>
+  <si>
+    <t>[ 2.27,  6.45]</t>
+  </si>
+  <si>
+    <t>57.42***</t>
+  </si>
+  <si>
+    <t>[49.25, 66.94]</t>
+  </si>
+  <si>
+    <t>124.24***</t>
+  </si>
+  <si>
+    <t>[110.38, 139.52]</t>
+  </si>
+  <si>
+    <t>3.77***</t>
+  </si>
+  <si>
+    <t>[ 3.54, 4.00]</t>
+  </si>
+  <si>
+    <t>0.37**</t>
+  </si>
+  <si>
+    <t>[0.19,  0.67]</t>
+  </si>
+  <si>
+    <t>Within-Person Effects</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>1.56**</t>
+  </si>
+  <si>
+    <t>[ 1.17,  2.21]</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>[ 0.91,  1.03]</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>[  0.96,   1.08]</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>[-0.06, 0.08]</t>
+  </si>
+  <si>
+    <t>1.41*</t>
+  </si>
+  <si>
+    <t>[1.06,  2.05]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>1.85***</t>
+  </si>
+  <si>
+    <t>[ 1.36,  2.74]</t>
+  </si>
+  <si>
+    <t>[ 0.90,  1.03]</t>
+  </si>
+  <si>
+    <t>[  0.98,   1.06]</t>
+  </si>
+  <si>
+    <t>0.09*</t>
+  </si>
+  <si>
+    <t>[ 0.00, 0.17]</t>
+  </si>
+  <si>
+    <t>1.17</t>
+  </si>
+  <si>
+    <t>[0.78,  2.15]</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>0.61*</t>
+  </si>
+  <si>
+    <t>[ 0.37,  0.99]</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>[ 0.78,  1.05]</t>
+  </si>
+  <si>
+    <t>[  0.87,   1.07]</t>
+  </si>
+  <si>
+    <t>0.28***</t>
+  </si>
+  <si>
+    <t>[ 0.12, 0.44]</t>
+  </si>
+  <si>
+    <t>1.40</t>
+  </si>
+  <si>
+    <t>[0.49,  4.04]</t>
+  </si>
+  <si>
+    <t>Own action plan</t>
+  </si>
+  <si>
+    <t>Partner action plan</t>
+  </si>
+  <si>
+    <t>Daily wear time</t>
+  </si>
+  <si>
+    <t>1.00**</t>
+  </si>
+  <si>
+    <t>[  1.00,   1.00]</t>
+  </si>
+  <si>
+    <t>Between-Person Effects</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>0.47**</t>
+  </si>
+  <si>
+    <t>[ 0.25,  0.83]</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>[ 0.99,  1.72]</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>[  0.82,   1.17]</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>[-0.21, 0.45]</t>
+  </si>
+  <si>
+    <t>10.98***</t>
+  </si>
+  <si>
+    <t>[3.14, 58.14]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>[ 0.32,  1.10]</t>
+  </si>
+  <si>
+    <t>[ 0.89,  1.55]</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>[  0.87,   1.25]</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>[-0.22, 0.43]</t>
+  </si>
+  <si>
+    <t>2.03</t>
+  </si>
+  <si>
+    <t>[0.51,  8.60]</t>
+  </si>
+  <si>
+    <t>Mean wear time</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t>L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>1.24</t>
+  </si>
+  <si>
+    <t>[0.90, 1.73]</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>[0.27, 0.50]</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>[0.08, 0.37]</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>[0.31, 0.73]</t>
+  </si>
+  <si>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>[0.38, 2.29]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>[0.07, 1.05]</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>[0.00, 0.16]</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>[0.03, 0.18]</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>[0.01, 0.17]</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>[0.01, 0.70]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>[0.09, 1.13]</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>[0.01, 0.18]</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>[0.00, 0.10]</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>[0.07, 0.25]</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>[0.04, 1.17]</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t>L2:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>[0.01, 0.61]</t>
+  </si>
+  <si>
+    <t>[0.01, 0.21]</t>
+  </si>
+  <si>
+    <t>[0.17, 0.35]</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>[0.38, 0.66]</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>[0.59, 2.33]</t>
+  </si>
+  <si>
+    <t>Additional Parameters</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>[0.64, 0.70]</t>
+  </si>
+  <si>
+    <t>[0.50, 0.54]</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>[0.81, 0.88]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -483,16 +490,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i/>
     </font>
   </fonts>
   <fills count="2">
@@ -512,20 +519,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -538,20 +553,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -833,46 +863,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -907,7 +950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -942,7 +985,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -977,43 +1020,43 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="1"/>
@@ -1027,8 +1070,8 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="1"/>
@@ -1042,8 +1085,8 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="1"/>
@@ -1057,8 +1100,8 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="1"/>
@@ -1072,8 +1115,8 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -1107,8 +1150,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1142,8 +1185,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -1177,8 +1220,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B13" s="1"/>
@@ -1192,8 +1235,8 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B14" s="1"/>
@@ -1207,8 +1250,8 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="1"/>
@@ -1226,43 +1269,43 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B17" s="1"/>
@@ -1276,8 +1319,8 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B18" s="1"/>
@@ -1291,8 +1334,8 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B19" s="1"/>
@@ -1306,8 +1349,8 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>72</v>
       </c>
       <c r="B20" s="1"/>
@@ -1321,8 +1364,8 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>73</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1356,8 +1399,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1391,8 +1434,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B23" s="1"/>
@@ -1410,43 +1453,43 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1480,8 +1523,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>108</v>
       </c>
       <c r="B26" s="1"/>
@@ -1495,8 +1538,8 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>109</v>
       </c>
       <c r="B27" s="1"/>
@@ -1510,8 +1553,8 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>110</v>
       </c>
       <c r="B28" s="1"/>
@@ -1525,8 +1568,8 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>111</v>
       </c>
       <c r="B29" s="1"/>
@@ -1540,8 +1583,8 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>112</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -1575,8 +1618,8 @@
         <v>122</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>123</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1610,43 +1653,43 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="10" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
         <v>135</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -1680,43 +1723,43 @@
         <v>142</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" s="10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>144</v>
       </c>
       <c r="B35" s="4"/>
@@ -1742,37 +1785,37 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36">
-      <c r="A36" s="7"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7"/>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A34:K34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Output/AllModels_SensitivityOnlyPushing_12000.xlsx
+++ b/Output/AllModels_SensitivityOnlyPushing_12000.xlsx
@@ -1,482 +1,421 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kueng\DataAnalysis\02TimeAndTiesControl\Output\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A4AB3A-7956-4524-82EE-CA08C4AB0C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="150">
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Subjective MVPA Hurdle Lognormal</t>
-  </si>
-  <si>
-    <t>Device-Based MVPA Log (Gaussian)</t>
-  </si>
-  <si>
-    <t>Mood Gaussian</t>
-  </si>
-  <si>
-    <t>Reactance Dichotome</t>
-  </si>
-  <si>
-    <t>Hurdle</t>
-  </si>
-  <si>
-    <t>Non-Zero</t>
-  </si>
-  <si>
-    <t>exp(Est.)_hu pa_sub</t>
-  </si>
-  <si>
-    <t>95% CI_hu pa_sub</t>
-  </si>
-  <si>
-    <t>exp(Est.)_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t>95% CI_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t>exp(Est.) pa_obj_log</t>
-  </si>
-  <si>
-    <t>95% CI pa_obj_log</t>
-  </si>
-  <si>
-    <t>Est. mood_gauss</t>
-  </si>
-  <si>
-    <t>95% CI mood_gauss</t>
-  </si>
-  <si>
-    <t>OR is_reactance</t>
-  </si>
-  <si>
-    <t>95% CI is_reactance</t>
-  </si>
-  <si>
-    <t>Intercept</t>
-  </si>
-  <si>
-    <t>3.80***</t>
-  </si>
-  <si>
-    <t>[ 2.27,  6.45]</t>
-  </si>
-  <si>
-    <t>57.42***</t>
-  </si>
-  <si>
-    <t>[49.25, 66.94]</t>
-  </si>
-  <si>
-    <t>124.24***</t>
-  </si>
-  <si>
-    <t>[110.38, 139.52]</t>
-  </si>
-  <si>
-    <t>3.77***</t>
-  </si>
-  <si>
-    <t>[ 3.54, 4.00]</t>
-  </si>
-  <si>
-    <t>0.37**</t>
-  </si>
-  <si>
-    <t>[0.19,  0.67]</t>
-  </si>
-  <si>
-    <t>Within-Person Effects</t>
-  </si>
-  <si>
-    <t>Daily individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t>Daily partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t>Daily individual's experienced pressure</t>
-  </si>
-  <si>
-    <t>Daily partner's experienced pressure</t>
-  </si>
-  <si>
-    <t>Daily individual's experienced pushing</t>
-  </si>
-  <si>
-    <t>1.56**</t>
-  </si>
-  <si>
-    <t>[ 1.17,  2.21]</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>[ 0.91,  1.03]</t>
-  </si>
-  <si>
-    <t>1.02</t>
-  </si>
-  <si>
-    <t>[  0.96,   1.08]</t>
-  </si>
-  <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>[-0.06, 0.08]</t>
-  </si>
-  <si>
-    <t>1.41*</t>
-  </si>
-  <si>
-    <t>[1.06,  2.05]</t>
-  </si>
-  <si>
-    <t>Daily partner's experienced pushing</t>
-  </si>
-  <si>
-    <t>1.85***</t>
-  </si>
-  <si>
-    <t>[ 1.36,  2.74]</t>
-  </si>
-  <si>
-    <t>[ 0.90,  1.03]</t>
-  </si>
-  <si>
-    <t>[  0.98,   1.06]</t>
-  </si>
-  <si>
-    <t>0.09*</t>
-  </si>
-  <si>
-    <t>[ 0.00, 0.17]</t>
-  </si>
-  <si>
-    <t>1.17</t>
-  </si>
-  <si>
-    <t>[0.78,  2.15]</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>0.61*</t>
-  </si>
-  <si>
-    <t>[ 0.37,  0.99]</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>[ 0.78,  1.05]</t>
-  </si>
-  <si>
-    <t>[  0.87,   1.07]</t>
-  </si>
-  <si>
-    <t>0.28***</t>
-  </si>
-  <si>
-    <t>[ 0.12, 0.44]</t>
-  </si>
-  <si>
-    <t>1.40</t>
-  </si>
-  <si>
-    <t>[0.49,  4.04]</t>
-  </si>
-  <si>
-    <t>Own action plan</t>
-  </si>
-  <si>
-    <t>Partner action plan</t>
-  </si>
-  <si>
-    <t>Daily wear time</t>
-  </si>
-  <si>
-    <t>1.00**</t>
-  </si>
-  <si>
-    <t>[  1.00,   1.00]</t>
-  </si>
-  <si>
-    <t>Between-Person Effects</t>
-  </si>
-  <si>
-    <t>Mean individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t>Mean partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t>Mean individual's experienced pressure</t>
-  </si>
-  <si>
-    <t>Mean partner's experienced pressure</t>
-  </si>
-  <si>
-    <t>Mean individual's experienced pushing</t>
-  </si>
-  <si>
-    <t>0.47**</t>
-  </si>
-  <si>
-    <t>[ 0.25,  0.83]</t>
-  </si>
-  <si>
-    <t>1.31</t>
-  </si>
-  <si>
-    <t>[ 0.99,  1.72]</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>[  0.82,   1.17]</t>
-  </si>
-  <si>
-    <t>0.12</t>
-  </si>
-  <si>
-    <t>[-0.21, 0.45]</t>
-  </si>
-  <si>
-    <t>10.98***</t>
-  </si>
-  <si>
-    <t>[3.14, 58.14]</t>
-  </si>
-  <si>
-    <t>Mean partner's experienced pushing</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>[ 0.32,  1.10]</t>
-  </si>
-  <si>
-    <t>[ 0.89,  1.55]</t>
-  </si>
-  <si>
-    <t>1.04</t>
-  </si>
-  <si>
-    <t>[  0.87,   1.25]</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>[-0.22, 0.43]</t>
-  </si>
-  <si>
-    <t>2.03</t>
-  </si>
-  <si>
-    <t>[0.51,  8.60]</t>
-  </si>
-  <si>
-    <t>Mean wear time</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Random Effects (Level 3 - Couple)</t>
-  </si>
-  <si>
-    <t>L3:sd(Intercept)</t>
-  </si>
-  <si>
-    <t>1.24</t>
-  </si>
-  <si>
-    <t>[0.90, 1.73]</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>[0.27, 0.50]</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>[0.08, 0.37]</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>[0.31, 0.73]</t>
-  </si>
-  <si>
-    <t>1.38</t>
-  </si>
-  <si>
-    <t>[0.38, 2.29]</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>[0.07, 1.05]</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>[0.00, 0.16]</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>[0.03, 0.18]</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>[0.01, 0.17]</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>[0.01, 0.70]</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>[0.09, 1.13]</t>
-  </si>
-  <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>[0.01, 0.18]</t>
-  </si>
-  <si>
-    <t>0.03</t>
-  </si>
-  <si>
-    <t>[0.00, 0.10]</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>[0.07, 0.25]</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>[0.04, 1.17]</t>
-  </si>
-  <si>
-    <t>Random Effects (Level 2 - Couple:Person)</t>
-  </si>
-  <si>
-    <t>L2:sd(Intercept)</t>
-  </si>
-  <si>
-    <t>[0.01, 0.61]</t>
-  </si>
-  <si>
-    <t>[0.01, 0.21]</t>
-  </si>
-  <si>
-    <t>[0.17, 0.35]</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>[0.38, 0.66]</t>
-  </si>
-  <si>
-    <t>1.32</t>
-  </si>
-  <si>
-    <t>[0.59, 2.33]</t>
-  </si>
-  <si>
-    <t>Additional Parameters</t>
-  </si>
-  <si>
-    <t>sigma</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>[0.64, 0.70]</t>
-  </si>
-  <si>
-    <t>[0.50, 0.54]</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>[0.81, 0.88]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Subjective MVPA Hurdle Lognormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device-Based MVPA Log (Gaussian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mood Gaussian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactance Dichotome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp(Est.)_hu pa_sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI_hu pa_sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp(Est.)_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp(Est.) pa_obj_log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI pa_obj_log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. mood_gauss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI mood_gauss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR is_reactance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI is_reactance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 2.32,  6.72]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.49***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[48.38, 65.73]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.93***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[109.86, 139.41]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 3.57, 3.98]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.21,  0.70]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within-Person Effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily individual's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily individual's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.23,  2.28]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.92,  1.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.97,   1.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.05, 0.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.05,  1.96]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.42,  3.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.93,  1.04]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.98,   1.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.02, 0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.73,  1.47]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.36,  0.97]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.78,  1.05]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.88,   1.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.11, 0.44]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.49,  4.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own action plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner action plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily wear time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  1.00,   1.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Between-Person Effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.24,  0.85]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.94,  1.58]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.82,   1.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.15, 0.48]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.13***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2.96, 51.93]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.31,  1.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.84,  1.42]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.87,   1.25]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.27, 0.36]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.53,  8.69]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean wear time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.93, 1.77]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.26, 0.49]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.13, 0.37]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 0.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.29, 2.28]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.22]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.17, 0.34]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.43, 0.78]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.45, 2.33]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional Parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.64, 0.70]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.50, 0.54]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.81, 0.88]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -490,16 +429,16 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <b/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <i/>
     </font>
   </fonts>
   <fills count="2">
@@ -519,28 +458,20 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -553,35 +484,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -863,59 +779,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -950,7 +853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -985,7 +888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1020,43 +923,43 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5">
+      <c r="A5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6">
+      <c r="A6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="1"/>
@@ -1070,8 +973,8 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="7">
+      <c r="A7" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="1"/>
@@ -1085,8 +988,8 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="8">
+      <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="1"/>
@@ -1100,8 +1003,8 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9">
+      <c r="A9" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="1"/>
@@ -1115,8 +1018,8 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10">
+      <c r="A10" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -1150,8 +1053,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11">
+      <c r="A11" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1161,68 +1064,68 @@
         <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
         <v>53</v>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="B12" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1235,9 +1138,9 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>64</v>
+    <row r="14">
+      <c r="A14" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1250,63 +1153,63 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>65</v>
+    <row r="15">
+      <c r="A15" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+    <row r="16">
+      <c r="A16" s="6" t="s">
         <v>69</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1319,9 +1222,9 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>70</v>
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1334,9 +1237,9 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>71</v>
+    <row r="19">
+      <c r="A19" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1349,9 +1252,9 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>72</v>
+    <row r="20">
+      <c r="A20" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1364,24 +1267,24 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>73</v>
+    <row r="21">
+      <c r="A21" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>79</v>
@@ -1399,8 +1302,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+    <row r="22">
+      <c r="A22" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1410,86 +1313,86 @@
         <v>86</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+    <row r="24">
+      <c r="A24" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+    <row r="25">
+      <c r="A25" s="7" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1523,8 +1426,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+    <row r="26">
+      <c r="A26" s="7" t="s">
         <v>108</v>
       </c>
       <c r="B26" s="1"/>
@@ -1538,8 +1441,8 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+    <row r="27">
+      <c r="A27" s="7" t="s">
         <v>109</v>
       </c>
       <c r="B27" s="1"/>
@@ -1553,8 +1456,8 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+    <row r="28">
+      <c r="A28" s="7" t="s">
         <v>110</v>
       </c>
       <c r="B28" s="1"/>
@@ -1568,8 +1471,8 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+    <row r="29">
+      <c r="A29" s="7" t="s">
         <v>111</v>
       </c>
       <c r="B29" s="1"/>
@@ -1583,239 +1486,199 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+    <row r="30">
+      <c r="A30" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F33" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="I33" s="1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>144</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
+    <row r="36">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A34:K34"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A34:K34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Output/AllModels_SensitivityOnlyPushing_12000.xlsx
+++ b/Output/AllModels_SensitivityOnlyPushing_12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -338,24 +338,6 @@
     <t xml:space="preserve">[0.29, 2.28]</t>
   </si>
   <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
   </si>
   <si>
@@ -384,6 +366,81 @@
   </si>
   <si>
     <t xml:space="preserve">[0.45, 2.33]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 1.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.20]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.88]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 1.41]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.06, 0.22]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.93]</t>
   </si>
   <si>
     <t xml:space="preserve">Additional Parameters</t>
@@ -471,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -489,6 +546,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
@@ -1427,38 +1487,78 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1473,7 +1573,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1488,7 +1588,7 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1503,7 +1603,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1517,133 +1617,133 @@
       <c r="K31" s="1"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="s">
-        <v>114</v>
+      <c r="A32" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="s">
-        <v>125</v>
+      <c r="A35" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
@@ -1675,7 +1775,7 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A26:K26"/>
     <mergeCell ref="A34:K34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
